--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MISSISSIPPI_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/MISSISSIPPI_2011.xlsx
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C96">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C279">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C526">
